--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6232F49F-228B-461C-9009-FFB16A4ED7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796C085D-37BF-4B0F-B4E4-9E7FB52A7DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="0" windowWidth="11595" windowHeight="10350" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="450" windowWidth="11355" windowHeight="10350" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tong_quan" sheetId="1" r:id="rId1"/>
@@ -445,9 +445,6 @@
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -482,6 +479,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -756,58 +756,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>46286</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>5</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>5</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -837,226 +837,226 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="7"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>60</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <f>COUNTA(A2:A200)</f>
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>10</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <f>IFERROR(ROUND(AVERAGE(C2:C200),1),0)</f>
-        <v>38.200000000000003</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>30</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>30</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>2</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="6">
-        <v>15</v>
+      <c r="C8" s="5">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>30</v>
       </c>
     </row>
@@ -1091,106 +1091,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>10</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>15</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>10</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1220,115 +1220,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="12">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="12">
+      <c r="A7" s="11">
         <v>5</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>6</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="12">
+      <c r="A9" s="11">
         <v>7</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12">
+      <c r="A10" s="11">
         <v>8</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="12">
+      <c r="A11" s="11">
         <v>9</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12">
+      <c r="A12" s="11">
         <v>10</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="12" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="12">
+      <c r="A13" s="11">
         <v>11</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>92</v>
       </c>
     </row>
